--- a/output/laminas_comunales/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Pedro ( 14,2). Bajo umbral: Independencia ( -9,2); Calera de Tango (-28,0); Santiago ( -7,9); Conchalí ( -7,6); El Bosque ( -7,7); Estación Central ( -7,9); y 6 más.</t>
         </is>
       </c>
     </row>
